--- a/www/download/COUNTRY.LTU.rpPE.xlsx
+++ b/www/download/COUNTRY.LTU.rpPE.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>Lituânia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>3.99999999710861</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4.00000001825342</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3.99999998659746</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3.9999999995881</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3.99999999559562</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3.99999999588469</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3.99999999905712</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3.6655545966935</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3.05558102643111</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2.77785491279575</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2.76969939037289</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2.74982120464169</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2.52016123792344</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>2.34585943266422</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>2.47782342361756</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>10.9373346409289</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.493</t>
+          <t>8.17946534448587</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.502</t>
+          <t>6.34347806402666</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>5.08611301138489</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.457</t>
+          <t>5.06213506205196</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.399</t>
+          <t>5.69606638962269</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.346</t>
+          <t>5.19295335428975</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.395</t>
+          <t>4.36935485556181</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.426</t>
+          <t>3.57379550290586</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1.426</t>
+          <t>3.009754389672</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1.461</t>
+          <t>2.92990537614582</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>1.488</t>
+          <t>2.48114755457735</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>1.529</t>
+          <t>2.24715777978389</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.531</t>
+          <t>1.84594086537064</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1.443</t>
+          <t>2.17215700517948</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.203</t>
+          <t>8.20865559608208</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.149</t>
+          <t>5.96473676264086</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.148</t>
+          <t>4.51478867003951</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.187</t>
+          <t>3.80703961136416</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.165</t>
+          <t>3.8089738444475</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.124</t>
+          <t>4.08245985673168</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.078</t>
+          <t>3.5718651706936</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.113</t>
+          <t>3.03386317109992</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.133</t>
+          <t>2.16996359554948</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.159</t>
+          <t>1.90122334279473</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.211</t>
+          <t>1.82003352441301</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.252</t>
+          <t>1.49348517159306</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1.319</t>
+          <t>1.2389665499611</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>1.01820221531979</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.243</t>
+          <t>1.27266944800977</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2571.545</t>
+          <t>2.58004884694521</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2595.514</t>
+          <t>1.69856248381302</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2602.912</t>
+          <t>1.09884494402973</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2659.424</t>
+          <t>0.811303703723472</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2522.551</t>
+          <t>0.805258516831358</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2583.224</t>
+          <t>0.846861618000531</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2464.605</t>
+          <t>0.610570443063499</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2513.641</t>
+          <t>0.44989159336117</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2546.154</t>
+          <t>0.0406171439090792</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2578.763</t>
+          <t>0.0748046957973199</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2732.644</t>
+          <t>0.0620793380042577</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2760.572</t>
+          <t>-0.0390830109514754</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2868.389</t>
+          <t>-0.240944191417694</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2915.074</t>
+          <t>-0.338800506746391</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2692.609</t>
+          <t>-0.283295098492195</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2087.973</t>
+          <t>13478175149.1408</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1988.28</t>
+          <t>12819554722.2379</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1990.438</t>
+          <t>11808237541.0069</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2076.019</t>
+          <t>12909896824.6557</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2016.758</t>
+          <t>12433447260.3502</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2079.554</t>
+          <t>13270844814.6903</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1980.536</t>
+          <t>12909043370.1813</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2019.223</t>
+          <t>12802764756.8835</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2053.925</t>
+          <t>12012113448.2809</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2112.124</t>
+          <t>12392054711.9801</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2274.689</t>
+          <t>12919308428.033</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2341.042</t>
+          <t>12481276694.5957</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2475.446</t>
+          <t>12216906223.6753</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2553.702</t>
+          <t>12395374828.9081</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2306.659</t>
+          <t>11001656615.8814</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>862003691.898881</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>1069918396.52735</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>36.54</t>
+          <t>1352166991.85402</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>35.41</t>
+          <t>1713361405.49617</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>34.46</t>
+          <t>1709084392.08655</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>34.66</t>
+          <t>1712617356.7307</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>34.17</t>
+          <t>1810460986.20763</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>34.57</t>
+          <t>2084661938.5762</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>34.26</t>
+          <t>2406597938.50795</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>36.66</t>
+          <t>2899066286.75236</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>37.96</t>
+          <t>3150366346.09588</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>3552428901.81319</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>38.38</t>
+          <t>3912986646.28034</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>39.19</t>
+          <t>4381356409.87214</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>40.14</t>
+          <t>3622833878.53675</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>55.12</t>
+          <t>34392782.3601281</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>26954934.039481</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>56.27</t>
+          <t>22442039.9823294</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>56.54</t>
+          <t>21461458.896106</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>58.35</t>
+          <t>22296613.6222463</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>58.44</t>
+          <t>22567688.4105096</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>58.97</t>
+          <t>20499660.0568196</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>58.8</t>
+          <t>17807782.2309958</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>57.92</t>
+          <t>13185051.8390264</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>57.11</t>
+          <t>10951297.5117025</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>56.25</t>
+          <t>9834082.22158973</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>56.21</t>
+          <t>8377748.51144106</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>54.52</t>
+          <t>6548162.66877647</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>5319500.83797555</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>6288354.42451371</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>26998.2743750222</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6.49</t>
+          <t>26659.0536336654</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>25351.8010982647</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>25871.285125968</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>7.19</t>
+          <t>24994.4902629122</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>26419.557535931</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>24306.3510926547</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>6.63</t>
+          <t>24327.1932130763</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>7.82</t>
+          <t>26270.2450819817</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>28904.8137844264</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>32845.1617777098</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>33503.3663557763</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>39252.383023802</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>42828.7727205696</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>36554.739102773</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>44.33</t>
+          <t>44470.2299372481</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44.01</t>
+          <t>42787.6406217456</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>38559.6045285699</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>39995.9107670714</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>38996.9126438436</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>42.56</t>
+          <t>40495.056342876</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>37997.5785735917</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>43.69</t>
+          <t>38691.0344003613</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>45.71</t>
+          <t>42086.800346638</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>45.63</t>
+          <t>45103.1873231046</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>46.93</t>
+          <t>50948.8176190991</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>47.24</t>
+          <t>52339.1352797793</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>60555.7148696946</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>49.51</t>
+          <t>69810.6043913586</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>51.32</t>
+          <t>57076.5407053401</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>53.32</t>
+          <t>9.03629094775529</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>53.65</t>
+          <t>6.67867146201327</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>53.92</t>
+          <t>5.07886583934794</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>54.09</t>
+          <t>4.14783077629748</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>55.74</t>
+          <t>4.15792388237243</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>55.19</t>
+          <t>4.58108796342612</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>4.08965266350539</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>3.4681473174744</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>52.17</t>
+          <t>2.61560680227513</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>52.27</t>
+          <t>2.30774077213938</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>51.12</t>
+          <t>2.24885982191789</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>50.85</t>
+          <t>1.87485426611691</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>48.96</t>
+          <t>1.61302037218244</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>1.3409725540921</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>47.08</t>
+          <t>1.6571507787027</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>1392.3987857604</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1577.94541662314</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1859.27887218759</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>1957.24631743657</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>1970.09256789277</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2092.75656972439</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2353.13364660797</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2649.18477311275</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>3237.88281306627</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>3838.67502997525</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>4438.3889803169</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>5125.08748123012</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>6478.83406944057</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>7785.76745287189</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>7146.10989932949</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3.99999999710861</t>
+          <t>716.783379260669</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4.00000001825342</t>
+          <t>930.930476400721</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3.99999998659746</t>
+          <t>1177.64064784359</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>3.9999999995881</t>
+          <t>1444.04669658337</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3.99999999559562</t>
+          <t>1467.15116498115</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.99999999588469</t>
+          <t>1523.95208821027</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3.99999999905712</t>
+          <t>1678.68427093892</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>3.6655545966935</t>
+          <t>1873.17992503927</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>3.05558102643111</t>
+          <t>2123.90604404549</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2.77785491279575</t>
+          <t>2501.78312629648</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2.76969939037289</t>
+          <t>2602.10320153289</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2.74982120464169</t>
+          <t>2837.17666465393</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2.52016123792344</t>
+          <t>2966.40637273925</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2.34585943266422</t>
+          <t>3260.4229869565</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2.47782342361756</t>
+          <t>2913.42307766862</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-1045967096.96203</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-961394066.759308</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>-889069163.46316</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-792241114.820798</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-368093718.836938</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-278459998.201186</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-151969788.220837</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-111124973.989953</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>151692014.596254</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>-51162468.0561254</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>-162526319.514882</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>-208095774.608706</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>-297220173.675405</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>91452411.980972</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>177386067.22864</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-1174562092.84242</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>-1106401760.11738</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-1057733318.92791</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-950459797.096812</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-506617344.29499</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-468140829.673753</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-405642892.628864</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>-442897695.281202</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>-211888469.512499</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-418018270.794937</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>-634359978.374132</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>-722903000.131499</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>-936591404.389885</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>-446892261.159097</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>-441058335.18975</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>128594995.880392</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>145007693.358067</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>168664155.464754</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>158218682.276014</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>138523625.458053</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>189680831.472567</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>253673104.408027</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>331772721.291249</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>363580484.108752</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>366855802.738812</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>471833658.85925</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>514807225.522793</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>639371230.714479</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>538344673.140069</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>618444402.41839</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>7193.84654077531</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>7148.30928225663</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>7158.71950520401</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>7433.70802708258</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>7567.45403290682</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>8505.31065634843</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>8543.91987076888</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>8369.6438572111</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>7679.20914024415</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>8275.25004990117</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>8453.86854394414</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>8156.4694381077</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>7751.28028413947</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>7632.56072719613</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>7741.40439951761</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>8759.40833267154</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8549.09158773533</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>8492.29426134878</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>8896.44607815589</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>8775.27579051016</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>9852.28027989794</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>9842.34594545232</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>9568.91698849144</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>8641.63561619071</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>9410.73515554098</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>9719.79700417926</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>9438.55575983129</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>9055.2092827544</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>8943.73947213495</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>8979.81353259936</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1093.73</t>
+          <t>2785.35475277992</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>817.95</t>
+          <t>3540.9300159829</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>634.35</t>
+          <t>4435.34973971317</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>508.61</t>
+          <t>4160.90500981388</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>506.21</t>
+          <t>3524.99083892768</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>569.61</t>
+          <t>4403.01337789616</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>519.3</t>
+          <t>5178.13508376535</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>436.94</t>
+          <t>5887.63000237662</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>357.38</t>
+          <t>7706.11485602183</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>300.98</t>
+          <t>9118.8685379579</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>292.99</t>
+          <t>12140.3079666271</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>248.11</t>
+          <t>14416.2990549895</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>224.72</t>
+          <t>17142.913254606</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>184.59</t>
+          <t>23876.027783493</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>217.22</t>
+          <t>17610.1738120431</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>820.87</t>
+          <t>2874161369.86088</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>596.47</t>
+          <t>2715079888.73057</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>451.48</t>
+          <t>2803748842.73574</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>380.7</t>
+          <t>2766730039.80144</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>380.9</t>
+          <t>2534902015.07793</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>408.25</t>
+          <t>2998112848.61788</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>357.19</t>
+          <t>3132353723.9077</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>303.39</t>
+          <t>3143552030.88189</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>3064370657.12354</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>190.12</t>
+          <t>2790046703.33676</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>3260915839.89125</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>149.35</t>
+          <t>3268426384.88622</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>123.9</t>
+          <t>3077303016.52361</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>101.82</t>
+          <t>3322900363.34344</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>127.27</t>
+          <t>3053700644.52318</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>3526.51382046901</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>169.86</t>
+          <t>4409.395665596</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>109.88</t>
+          <t>5563.63210469451</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>81.13</t>
+          <t>5658.86379586788</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>80.53</t>
+          <t>4855.91104604275</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>84.69</t>
+          <t>5338.12529778591</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>61.06</t>
+          <t>6119.8313817904</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>44.99</t>
+          <t>7063.11434683333</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>9191.95625324947</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>11091.372515054</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>14441.4051098642</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-3.91</t>
+          <t>17761.9081874317</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-24.09</t>
+          <t>22277.3042327746</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-33.88</t>
+          <t>29376.4381969645</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-28.33</t>
+          <t>18317.813610085</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>12965.676</t>
+          <t>2113916902.27534</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>12768.068</t>
+          <t>2076990252.21702</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>12759.672</t>
+          <t>2307024895.29833</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>13259.263</t>
+          <t>2553155610.83178</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>12787.332</t>
+          <t>2712254066.96623</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>13785.311</t>
+          <t>3124657504.78394</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>13246.813</t>
+          <t>3412114178.37103</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>13347.682</t>
+          <t>3562606693.59381</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>12322.108</t>
+          <t>3799631265.87103</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>13415.003</t>
+          <t>3489148968.20704</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>14197.707</t>
+          <t>3897539539.65613</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>14040.796</t>
+          <t>4104586028.05633</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>13844.509</t>
+          <t>4126169797.45437</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>13690.562</t>
+          <t>4667671149.02319</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>12956.811</t>
+          <t>3411609219.47036</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>8651.32</t>
+          <t>-741.15906768909</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8215.552</t>
+          <t>-868.465649613101</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>8219.642</t>
+          <t>-1128.28236498135</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>8820.095</t>
+          <t>-1497.958786054</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>8815.327</t>
+          <t>-1330.92020711507</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>9558.268</t>
+          <t>-935.11191988976</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>9214.618</t>
+          <t>-941.696298025052</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>9314.577</t>
+          <t>-1175.48434445671</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>8701.312</t>
+          <t>-1485.84139722765</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>9589.36</t>
+          <t>-1972.50397709605</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>10235.099</t>
+          <t>-2301.09714323712</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>10212.715</t>
+          <t>-3345.60913244218</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>10224.714</t>
+          <t>-5134.39097816862</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>10256.635</t>
+          <t>-5500.41041347152</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>9626.416</t>
+          <t>-707.639798041871</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>13478.175</t>
+          <t>760244467.585536</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>12819.555</t>
+          <t>638089636.513552</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>11808.238</t>
+          <t>496723947.437411</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>12909.897</t>
+          <t>213574428.96966</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>12433.447</t>
+          <t>-177352051.888296</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>13270.845</t>
+          <t>-126544656.166061</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>12909.043</t>
+          <t>-279760454.463327</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>12802.765</t>
+          <t>-419054662.711925</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>12012.113</t>
+          <t>-735260608.747496</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>12392.055</t>
+          <t>-699102264.870274</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>12919.308</t>
+          <t>-636623699.764871</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>12481.277</t>
+          <t>-836159643.170114</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>12216.906</t>
+          <t>-1048866780.93076</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>12395.375</t>
+          <t>-1344770785.67975</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>11001.657</t>
+          <t>-357908574.947185</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>3247.55</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>4107.62498</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>4884.125</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>5344.84999</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>5082.15008</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>5179.55</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>5518.45004</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>6309.08615</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>8480.41658</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>10617.22104</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>12152.58224</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>13964.39876</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>17812.98732</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>21228.38204</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>15968.43085</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>8182.721</t>
+          <t>0.0687741897736268</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>7987.288</t>
+          <t>0.0576937410506823</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>7763.567</t>
+          <t>0.0721409061041283</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>8350.744</t>
+          <t>0.0752591958343908</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>7969.033</t>
+          <t>0.071798425050771</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8658.09</t>
+          <t>0.0886671422505292</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>8257.677</t>
+          <t>0.0896006143369258</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>8049.806</t>
+          <t>0.096398292779201</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>7497.865</t>
+          <t>0.1068456720524</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>7941.568</t>
+          <t>0.108786705094041</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>8328.687</t>
+          <t>0.110923465021113</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>7989.524</t>
+          <t>0.104226380077007</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>7919.033</t>
+          <t>0.101543666623191</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>7604.557</t>
+          <t>0.0939490246155326</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>7046.024</t>
+          <t>0.0714930308406639</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>2504.97500744375</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>3185.72497070167</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>3915.82503481901</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>4674.57499957807</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>4707.72500997286</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>4508.299991816</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>4631.35001721752</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>5473.03260370754</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>7280.6121051987</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>9086.21960703123</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>10621.4053437327</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>12904.6207284722</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>16887.3322519144</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>21323.5323202352</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>16682.5566681587</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>862.004</t>
+          <t>2931.45183109582</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1069.918</t>
+          <t>4413.2116762702</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1352.167</t>
+          <t>4810.78304557858</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1713.361</t>
+          <t>5513.89748690017</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1709.084</t>
+          <t>5373.96564117383</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1712.617</t>
+          <t>5163.52928834904</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1810.461</t>
+          <t>5423.21665241783</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2084.662</t>
+          <t>6355.59458427306</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2406.598</t>
+          <t>8402.73777334017</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2899.066</t>
+          <t>10486.1630721106</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>3150.366</t>
+          <t>12126.7510595509</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>3552.429</t>
+          <t>14490.2804927815</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>3912.987</t>
+          <t>19059.9184852712</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>4381.356</t>
+          <t>23934.7048099527</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>3622.834</t>
+          <t>18804.4211754875</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>903.63</t>
+          <t>24600.7898997101</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>667.87</t>
+          <t>27546.6244373116</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>507.89</t>
+          <t>30603.485199467</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>414.78</t>
+          <t>31813.1379045267</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>415.79</t>
+          <t>32026.7029437954</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>458.11</t>
+          <t>32640.4917139336</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>408.97</t>
+          <t>33887.0412155523</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>346.81</t>
+          <t>37548.8012106701</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>261.56</t>
+          <t>47207.3276034981</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>230.77</t>
+          <t>55893.2189614342</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>224.89</t>
+          <t>62765.6060762895</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>187.49</t>
+          <t>72359.252719093</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>161.3</t>
+          <t>93978.2073332064</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>134.1</t>
+          <t>115669.457151328</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>165.72</t>
+          <t>102329.524978285</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>34.393</t>
+          <t>2931.45183109582</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>26.955</t>
+          <t>3647.69272428469</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>22.442</t>
+          <t>3627.32457554207</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>21.461</t>
+          <t>3993.82412836323</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>22.297</t>
+          <t>3970.65942851008</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>22.568</t>
+          <t>3851.35197013299</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>4095.94484300415</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>17.808</t>
+          <t>4385.76814554866</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>13.185</t>
+          <t>4887.15773120033</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>10.951</t>
+          <t>5340.7093261259</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>9.834</t>
+          <t>5713.95903946836</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>8.378</t>
+          <t>6311.66165310784</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>6.548</t>
+          <t>7067.72863079353</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>7387.65518169046</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>6.288</t>
+          <t>6483.95376910765</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2504.97500744375</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2657.11121643758</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2939.42878253037</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>3329.00648439264</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>3412.31095538772</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>3237.98370956394</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3330.82440010191</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>3612.69539104058</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>4043.94705554353</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>4417.79952482758</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>4874.89543464886</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>5542.76286926896</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>6135.93360606634</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>6441.95147274622</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>5475.74598192922</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3084.29817890418</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>3167.2132337298</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>4067.04202442142</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>4351.47749309983</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>4269.55939882617</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>4986.89569165096</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5389.43335758217</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>6268.82510572694</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>8281.78145665983</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>9919.11415788945</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>11400.5674904491</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>12666.8304572185</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>16021.7258247288</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>18652.8001300473</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>14461.9577845125</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>8651319849.93638</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>8215551858.09755</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>8219641735.87524</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>8820094574.13348</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>8815327202.93316</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>9558268115.60436</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>9214617580.62424</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>9314576648.69024</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>8701311876.81064</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>9589359757.82547</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>10235098646.1532</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>10212715383.4547</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>10224713822.8084</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>10256635105.2062</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>9626415861.46445</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>12965676214.0204</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>12768068286.2827</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>12759672127.6765</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>13259263234.8835</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>12787331881.9314</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>13785310567.6332</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>13246813407.9843</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>13347682307.2467</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>12322108225.1263</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>13415002964.2237</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>14197707484.0046</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>14040795548.325</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>13844509472.4032</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>13690562003.4442</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>12956810780.6779</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>8182720693.47498</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>7987287729.2084</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>7763567420.37812</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>8350744245.89615</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>7969032813.48135</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>8658090142.2502</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>8257677257.4662</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>8049806285.33834</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>7497865402.92593</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>7941568104.49453</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>8328687400.50609</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>7989524157.24004</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>7919032637.78597</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>7604556585.09226</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>7046024204.02494</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1480200</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1493500</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1502500</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1490400</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1457200</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>1399200</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1345900</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1394900</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1425900</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1425500</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1460700</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1487600</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1528900</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>1530742.48708814</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1442881.941105</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1202600</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1149300</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1148200</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1186500</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1164900</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1123800</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1078500</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1112900</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1133100</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1158800</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>1210700</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1252100</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1319100</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>1343800</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1243497.35069574</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2571545000</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2595513640.41746</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2602912000</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2659424000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2522551000</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2583224000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2464604694.9485</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2513640732.24568</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2546154000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2578763000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2732644442.90056</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2760571519.06275</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2868389000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>2915073729.0729</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2692608724.27263</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2087973000</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1988280000</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1990438000</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2076018674.27178</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2016758000</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2079554000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1980536270.47619</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2019223254.9505</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2053925000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2112123969.96663</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2274689000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2341041784.49537</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>2475446000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2553701952.54095</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2306658737.99467</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.38297454039357</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.374950919159893</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.365446441330267</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.354082269774032</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.344615980455163</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.346596133326365</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.34174830988491</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.345725669120357</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.342606166961938</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.366551899886692</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.379590543195016</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.382423371633458</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.383804148482609</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.391863244594682</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.401402104157042</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.551165908038753</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.56012188209631</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.562656144083645</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.565446055716564</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.58347578064208</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.584354733603416</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.589745862974171</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.587979910136802</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.579241250905231</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.571140274425083</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.562470444100666</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.562069271680628</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.545168024157812</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.543979820692733</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.532984201290888</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.0658595515676768</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.0649271987437972</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.0718974145860885</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.0804716745094041</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.0719082389027571</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.0690491330702188</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.0685058271409187</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.0662944207428411</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.0781525821328311</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.0623078256882247</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.0579390127043173</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.0555073566859132</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.0710278273595789</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0641569347125852</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.0656136945520701</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.443293040487766</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.44011394011716</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.435028528549326</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.431579171849232</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.418473428162359</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.425554961483175</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.42804749122567</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.436917122786728</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.457087834938123</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.456304958443269</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.46929694022081</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.472379654022888</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.488436427417749</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.495064173032602</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.513168041746021</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.533195858273454</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.536466799619575</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.539169852517655</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.540934807250721</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.557361362849752</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.55194435073716</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.549960755868425</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.542033809430307</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.521658985016304</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.522657392183035</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.511183992718785</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.50845992883912</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.489568674628268</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.487523074893578</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.470849731791764</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.0235111012387795</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.0234192602632656</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.0258016189330191</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.0274860209000473</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.0241652089878893</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.0225006877796653</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.0219917529059049</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.0210490677829655</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.0212531800455728</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.0210376493736961</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.0195190670604044</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.0191604171379914</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.0219948979539834</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.01741275207382</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.0159822264622145</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>13012.95002</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>16011.72486</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>17948.70002</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>19579.40021</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>18273.80013</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>19248.7999</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>20729.19991</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>24205.77749</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>31550.79177</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>38827.22596</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>45762.79956</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>53512.71586</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>68779.84557</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>87380.2149</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>63756.94838</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>6015.75001</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>7580.42491</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>8877.82507</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>9865.37498</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>9643.52504</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>10150.42498</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10812.65001</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>12624.41969</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>16684.51923</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>20405.27723</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>23527.31855</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>27157.11095</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>35081.64431</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>42587.50494</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>33266.37896</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>98403.1598270781</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>101377.408978468</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>105819.601650491</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>111683.194777985</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>116521.856497935</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>120126.189828282</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>124588.862428806</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>129644.249343817</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>135812.082947234</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>143521.622402548</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>152146.281960362</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>163093.292643572</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>177643.798404054</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>190049.299326338</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>192823.545110645</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
